--- a/Data/EC/NIT-9006325466.xlsx
+++ b/Data/EC/NIT-9006325466.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5712FF5-5CA6-4752-BC22-4BB53835F9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D89DF95-9CE1-43B2-A85A-AB3DFEB72153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E3A63CBE-5C74-4B1F-8751-2AB1E33AE817}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3B49F944-E07D-4EB9-93A7-0FB1201A05E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="135">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,355 +71,343 @@
     <t>ENRIQUE RUIZ GOMEZ</t>
   </si>
   <si>
-    <t>2512</t>
-  </si>
-  <si>
-    <t>2511</t>
-  </si>
-  <si>
-    <t>2510</t>
-  </si>
-  <si>
-    <t>2509</t>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>PPT</t>
+  </si>
+  <si>
+    <t>2436958</t>
+  </si>
+  <si>
+    <t>OSMEL JESUS DIAZ GONZALEZ</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2507</t>
   </si>
   <si>
     <t>2508</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1607</t>
-  </si>
-  <si>
-    <t>PPT</t>
-  </si>
-  <si>
-    <t>2436958</t>
-  </si>
-  <si>
-    <t>OSMEL JESUS DIAZ GONZALEZ</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -518,7 +506,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -531,9 +521,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -727,29 +715,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -768,29 +756,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -843,7 +821,7 @@
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{588C8ABB-897D-A787-9DC9-D35951F2F922}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612B1EB2-8472-83BF-7D8B-26DE3E788F66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1194,8 +1172,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977C017B-6FFB-4E25-B306-286C2DAD9206}">
-  <dimension ref="B2:J136"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6948C09F-7812-42E2-9EE3-896BC8EE18FC}">
+  <dimension ref="B2:J132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.6328125" customWidth="1"/>
@@ -1212,57 +1190,57 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="3"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="29"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="6" t="s">
         <v>7</v>
       </c>
@@ -1278,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="29"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="6">
         <v>9006325466</v>
       </c>
@@ -1291,12 +1269,12 @@
     <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="29"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2734520</v>
+        <v>2640200</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1307,17 +1285,17 @@
     <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F13" s="5">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -1344,13 +1322,13 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
@@ -1363,18 +1341,18 @@
       <c r="D16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G16" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
+      <c r="F16" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G16" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="15" t="s">
@@ -1386,18 +1364,18 @@
       <c r="D17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G17" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
+      <c r="F17" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G17" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="15" t="s">
@@ -1409,18 +1387,18 @@
       <c r="D18" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G18" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
+      <c r="F18" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G18" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="15" t="s">
@@ -1432,18 +1410,18 @@
       <c r="D19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G19" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
+      <c r="F19" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G19" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="15" t="s">
@@ -1455,18 +1433,18 @@
       <c r="D20" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G20" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21"/>
+      <c r="F20" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G20" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="15" t="s">
@@ -1478,18 +1456,18 @@
       <c r="D21" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G21" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
+      <c r="F21" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G21" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="15" t="s">
@@ -1501,18 +1479,18 @@
       <c r="D22" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G22" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
+      <c r="F22" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G22" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="20"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="15" t="s">
@@ -1524,18 +1502,18 @@
       <c r="D23" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G23" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
+      <c r="F23" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G23" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="15" t="s">
@@ -1547,18 +1525,18 @@
       <c r="D24" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G24" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21"/>
+      <c r="F24" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G24" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="15" t="s">
@@ -1570,18 +1548,18 @@
       <c r="D25" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G25" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
+      <c r="F25" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G25" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="15" t="s">
@@ -1593,18 +1571,18 @@
       <c r="D26" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G26" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="21"/>
+      <c r="F26" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G26" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="15" t="s">
@@ -1616,18 +1594,18 @@
       <c r="D27" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G27" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="21"/>
+      <c r="F27" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G27" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="15" t="s">
@@ -1639,18 +1617,18 @@
       <c r="D28" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G28" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="21"/>
+      <c r="F28" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G28" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="20"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="15" t="s">
@@ -1662,18 +1640,18 @@
       <c r="D29" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G29" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="21"/>
+      <c r="F29" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G29" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="20"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="15" t="s">
@@ -1685,18 +1663,18 @@
       <c r="D30" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G30" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="21"/>
+      <c r="F30" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G30" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="20"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="15" t="s">
@@ -1708,18 +1686,18 @@
       <c r="D31" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F31" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G31" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="21"/>
+      <c r="F31" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G31" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="20"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="15" t="s">
@@ -1731,18 +1709,18 @@
       <c r="D32" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G32" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="21"/>
+      <c r="F32" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G32" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33" s="15" t="s">
@@ -1754,18 +1732,18 @@
       <c r="D33" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G33" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="21"/>
+      <c r="F33" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G33" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34" s="15" t="s">
@@ -1777,18 +1755,18 @@
       <c r="D34" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G34" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="21"/>
+      <c r="F34" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G34" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
@@ -1800,18 +1778,18 @@
       <c r="D35" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G35" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="21"/>
+      <c r="F35" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G35" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="20"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36" s="15" t="s">
@@ -1823,18 +1801,18 @@
       <c r="D36" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G36" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="21"/>
+      <c r="F36" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G36" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="20"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37" s="15" t="s">
@@ -1846,18 +1824,18 @@
       <c r="D37" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G37" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="21"/>
+      <c r="F37" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G37" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="20"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38" s="15" t="s">
@@ -1869,18 +1847,18 @@
       <c r="D38" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G38" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="21"/>
+      <c r="F38" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G38" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" s="15" t="s">
@@ -1892,18 +1870,18 @@
       <c r="D39" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G39" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="21"/>
+      <c r="F39" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G39" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B40" s="15" t="s">
@@ -1915,18 +1893,18 @@
       <c r="D40" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G40" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21"/>
+      <c r="F40" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G40" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B41" s="15" t="s">
@@ -1938,18 +1916,18 @@
       <c r="D41" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G41" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="21"/>
+      <c r="F41" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G41" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="20"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B42" s="15" t="s">
@@ -1961,18 +1939,18 @@
       <c r="D42" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G42" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="21"/>
+      <c r="F42" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G42" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B43" s="15" t="s">
@@ -1984,18 +1962,18 @@
       <c r="D43" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F43" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G43" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="21"/>
+      <c r="F43" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G43" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="20"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B44" s="15" t="s">
@@ -2007,18 +1985,18 @@
       <c r="D44" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F44" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G44" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="21"/>
+      <c r="F44" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G44" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="20"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B45" s="15" t="s">
@@ -2030,18 +2008,18 @@
       <c r="D45" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G45" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="21"/>
+      <c r="F45" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G45" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B46" s="15" t="s">
@@ -2053,18 +2031,18 @@
       <c r="D46" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G46" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="21"/>
+      <c r="F46" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G46" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="20"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B47" s="15" t="s">
@@ -2076,18 +2054,18 @@
       <c r="D47" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F47" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G47" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="21"/>
+      <c r="F47" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G47" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="20"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B48" s="15" t="s">
@@ -2099,18 +2077,18 @@
       <c r="D48" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F48" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G48" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="21"/>
+      <c r="F48" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G48" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="20"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49" s="15" t="s">
@@ -2122,18 +2100,18 @@
       <c r="D49" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G49" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="21"/>
+      <c r="F49" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G49" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50" s="15" t="s">
@@ -2145,18 +2123,18 @@
       <c r="D50" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F50" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G50" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="21"/>
+      <c r="F50" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G50" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B51" s="15" t="s">
@@ -2168,18 +2146,18 @@
       <c r="D51" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F51" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G51" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="21"/>
+      <c r="F51" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G51" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="20"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B52" s="15" t="s">
@@ -2191,18 +2169,18 @@
       <c r="D52" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E52" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F52" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G52" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="21"/>
+      <c r="F52" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G52" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="20"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B53" s="15" t="s">
@@ -2214,18 +2192,18 @@
       <c r="D53" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G53" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="21"/>
+      <c r="F53" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G53" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B54" s="15" t="s">
@@ -2237,18 +2215,18 @@
       <c r="D54" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="18" t="s">
+      <c r="E54" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F54" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G54" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="21"/>
+      <c r="F54" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G54" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="20"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55" s="15" t="s">
@@ -2260,18 +2238,18 @@
       <c r="D55" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F55" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G55" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="21"/>
+      <c r="F55" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G55" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="20"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56" s="15" t="s">
@@ -2283,18 +2261,18 @@
       <c r="D56" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="E56" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G56" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="21"/>
+      <c r="F56" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G56" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="20"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57" s="15" t="s">
@@ -2306,18 +2284,18 @@
       <c r="D57" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F57" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G57" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="21"/>
+      <c r="F57" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G57" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="20"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B58" s="15" t="s">
@@ -2329,18 +2307,18 @@
       <c r="D58" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F58" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G58" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="21"/>
+      <c r="F58" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G58" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B59" s="15" t="s">
@@ -2352,18 +2330,18 @@
       <c r="D59" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F59" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G59" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="21"/>
+      <c r="F59" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G59" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="20"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B60" s="15" t="s">
@@ -2375,18 +2353,18 @@
       <c r="D60" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G60" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="21"/>
+      <c r="F60" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G60" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="20"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B61" s="15" t="s">
@@ -2398,18 +2376,18 @@
       <c r="D61" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="F61" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G61" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="21"/>
+      <c r="F61" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G61" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="20"/>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B62" s="15" t="s">
@@ -2421,18 +2399,18 @@
       <c r="D62" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F62" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G62" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="21"/>
+      <c r="F62" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G62" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="20"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B63" s="15" t="s">
@@ -2444,18 +2422,18 @@
       <c r="D63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F63" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G63" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="21"/>
+      <c r="F63" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G63" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="20"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B64" s="15" t="s">
@@ -2467,18 +2445,18 @@
       <c r="D64" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E64" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F64" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G64" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="21"/>
+      <c r="F64" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G64" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20"/>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B65" s="15" t="s">
@@ -2490,18 +2468,18 @@
       <c r="D65" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F65" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G65" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="21"/>
+      <c r="F65" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G65" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="20"/>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B66" s="15" t="s">
@@ -2513,18 +2491,18 @@
       <c r="D66" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="18" t="s">
+      <c r="E66" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G66" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="21"/>
+      <c r="F66" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G66" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B67" s="15" t="s">
@@ -2536,18 +2514,18 @@
       <c r="D67" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="18" t="s">
+      <c r="E67" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F67" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G67" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="21"/>
+      <c r="F67" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G67" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="20"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B68" s="15" t="s">
@@ -2559,18 +2537,18 @@
       <c r="D68" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E68" s="18" t="s">
+      <c r="E68" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F68" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G68" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="21"/>
+      <c r="F68" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G68" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="20"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B69" s="15" t="s">
@@ -2582,18 +2560,18 @@
       <c r="D69" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F69" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G69" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="21"/>
+      <c r="F69" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G69" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="20"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B70" s="15" t="s">
@@ -2605,18 +2583,18 @@
       <c r="D70" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="18" t="s">
+      <c r="E70" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="F70" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G70" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="21"/>
+      <c r="F70" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G70" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="20"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B71" s="15" t="s">
@@ -2628,18 +2606,18 @@
       <c r="D71" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="18" t="s">
+      <c r="E71" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F71" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G71" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="21"/>
+      <c r="F71" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G71" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="20"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B72" s="15" t="s">
@@ -2651,18 +2629,18 @@
       <c r="D72" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="18" t="s">
+      <c r="E72" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G72" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="21"/>
+      <c r="F72" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G72" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B73" s="15" t="s">
@@ -2674,18 +2652,18 @@
       <c r="D73" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F73" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G73" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="21"/>
+      <c r="F73" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G73" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="20"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B74" s="15" t="s">
@@ -2697,18 +2675,18 @@
       <c r="D74" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E74" s="18" t="s">
+      <c r="E74" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F74" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G74" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="21"/>
+      <c r="F74" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G74" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="20"/>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B75" s="15" t="s">
@@ -2720,18 +2698,18 @@
       <c r="D75" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="18" t="s">
+      <c r="E75" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F75" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G75" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
-      <c r="J75" s="21"/>
+      <c r="F75" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G75" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="20"/>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76" s="15" t="s">
@@ -2743,18 +2721,18 @@
       <c r="D76" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="18" t="s">
+      <c r="E76" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="F76" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G76" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
-      <c r="J76" s="21"/>
+      <c r="F76" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G76" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B77" s="15" t="s">
@@ -2766,18 +2744,18 @@
       <c r="D77" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F77" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G77" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="21"/>
+      <c r="F77" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G77" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="20"/>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B78" s="15" t="s">
@@ -2789,18 +2767,18 @@
       <c r="D78" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E78" s="18" t="s">
+      <c r="E78" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F78" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G78" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="21"/>
+      <c r="F78" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G78" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="20"/>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B79" s="15" t="s">
@@ -2812,18 +2790,18 @@
       <c r="D79" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="18" t="s">
+      <c r="E79" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F79" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G79" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
-      <c r="J79" s="21"/>
+      <c r="F79" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G79" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="20"/>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B80" s="15" t="s">
@@ -2835,18 +2813,18 @@
       <c r="D80" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E80" s="18" t="s">
+      <c r="E80" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F80" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G80" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="21"/>
+      <c r="F80" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G80" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="20"/>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B81" s="15" t="s">
@@ -2858,18 +2836,18 @@
       <c r="D81" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E81" s="18" t="s">
+      <c r="E81" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F81" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G81" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="21"/>
+      <c r="F81" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G81" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="20"/>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B82" s="15" t="s">
@@ -2881,18 +2859,18 @@
       <c r="D82" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E82" s="18" t="s">
+      <c r="E82" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F82" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G82" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-      <c r="J82" s="21"/>
+      <c r="F82" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G82" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="20"/>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B83" s="15" t="s">
@@ -2904,18 +2882,18 @@
       <c r="D83" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F83" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G83" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="21"/>
+      <c r="F83" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G83" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="20"/>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B84" s="15" t="s">
@@ -2927,18 +2905,18 @@
       <c r="D84" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E84" s="18" t="s">
+      <c r="E84" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F84" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G84" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="21"/>
+      <c r="F84" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G84" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H84" s="19"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="20"/>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B85" s="15" t="s">
@@ -2950,18 +2928,18 @@
       <c r="D85" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F85" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G85" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="21"/>
+      <c r="F85" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G85" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="20"/>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B86" s="15" t="s">
@@ -2973,18 +2951,18 @@
       <c r="D86" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E86" s="18" t="s">
+      <c r="E86" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F86" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G86" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="21"/>
+      <c r="F86" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G86" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H86" s="19"/>
+      <c r="I86" s="19"/>
+      <c r="J86" s="20"/>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B87" s="15" t="s">
@@ -2996,18 +2974,18 @@
       <c r="D87" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="18" t="s">
+      <c r="E87" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="F87" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G87" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-      <c r="J87" s="21"/>
+      <c r="F87" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G87" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H87" s="19"/>
+      <c r="I87" s="19"/>
+      <c r="J87" s="20"/>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B88" s="15" t="s">
@@ -3019,18 +2997,18 @@
       <c r="D88" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="18" t="s">
+      <c r="E88" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="F88" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G88" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="21"/>
+      <c r="F88" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G88" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H88" s="19"/>
+      <c r="I88" s="19"/>
+      <c r="J88" s="20"/>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B89" s="15" t="s">
@@ -3042,18 +3020,18 @@
       <c r="D89" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E89" s="18" t="s">
+      <c r="E89" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F89" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G89" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H89" s="20"/>
-      <c r="I89" s="20"/>
-      <c r="J89" s="21"/>
+      <c r="F89" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G89" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H89" s="19"/>
+      <c r="I89" s="19"/>
+      <c r="J89" s="20"/>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B90" s="15" t="s">
@@ -3065,18 +3043,18 @@
       <c r="D90" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E90" s="18" t="s">
+      <c r="E90" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F90" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G90" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="21"/>
+      <c r="F90" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G90" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H90" s="19"/>
+      <c r="I90" s="19"/>
+      <c r="J90" s="20"/>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B91" s="15" t="s">
@@ -3088,18 +3066,18 @@
       <c r="D91" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E91" s="18" t="s">
+      <c r="E91" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="F91" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G91" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
-      <c r="J91" s="21"/>
+      <c r="F91" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G91" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H91" s="19"/>
+      <c r="I91" s="19"/>
+      <c r="J91" s="20"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B92" s="15" t="s">
@@ -3111,18 +3089,18 @@
       <c r="D92" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E92" s="18" t="s">
+      <c r="E92" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F92" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G92" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
-      <c r="J92" s="21"/>
+      <c r="F92" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G92" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H92" s="19"/>
+      <c r="I92" s="19"/>
+      <c r="J92" s="20"/>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B93" s="15" t="s">
@@ -3134,18 +3112,18 @@
       <c r="D93" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E93" s="18" t="s">
+      <c r="E93" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F93" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G93" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
-      <c r="J93" s="21"/>
+      <c r="F93" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G93" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H93" s="19"/>
+      <c r="I93" s="19"/>
+      <c r="J93" s="20"/>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B94" s="15" t="s">
@@ -3157,18 +3135,18 @@
       <c r="D94" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E94" s="18" t="s">
+      <c r="E94" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F94" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G94" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H94" s="20"/>
-      <c r="I94" s="20"/>
-      <c r="J94" s="21"/>
+      <c r="F94" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G94" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H94" s="19"/>
+      <c r="I94" s="19"/>
+      <c r="J94" s="20"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B95" s="15" t="s">
@@ -3180,18 +3158,18 @@
       <c r="D95" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="18" t="s">
+      <c r="E95" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F95" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G95" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H95" s="20"/>
-      <c r="I95" s="20"/>
-      <c r="J95" s="21"/>
+      <c r="F95" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G95" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H95" s="19"/>
+      <c r="I95" s="19"/>
+      <c r="J95" s="20"/>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B96" s="15" t="s">
@@ -3203,18 +3181,18 @@
       <c r="D96" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="18" t="s">
+      <c r="E96" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F96" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G96" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H96" s="20"/>
-      <c r="I96" s="20"/>
-      <c r="J96" s="21"/>
+      <c r="F96" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G96" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
+      <c r="J96" s="20"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B97" s="15" t="s">
@@ -3226,41 +3204,41 @@
       <c r="D97" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="E97" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="F97" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G97" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
-      <c r="J97" s="21"/>
+      <c r="F97" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G97" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="20"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B98" s="15" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F98" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G98" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
-      <c r="J98" s="21"/>
+        <v>95</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F98" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G98" s="18">
+        <v>1460000</v>
+      </c>
+      <c r="H98" s="19"/>
+      <c r="I98" s="19"/>
+      <c r="J98" s="20"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B99" s="15" t="s">
@@ -3272,18 +3250,18 @@
       <c r="D99" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E99" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F99" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G99" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
-      <c r="J99" s="21"/>
+      <c r="E99" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F99" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G99" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H99" s="19"/>
+      <c r="I99" s="19"/>
+      <c r="J99" s="20"/>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B100" s="15" t="s">
@@ -3295,18 +3273,18 @@
       <c r="D100" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E100" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F100" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G100" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
-      <c r="J100" s="21"/>
+      <c r="E100" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F100" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G100" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H100" s="19"/>
+      <c r="I100" s="19"/>
+      <c r="J100" s="20"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B101" s="15" t="s">
@@ -3318,18 +3296,18 @@
       <c r="D101" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E101" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F101" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G101" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H101" s="20"/>
-      <c r="I101" s="20"/>
-      <c r="J101" s="21"/>
+      <c r="E101" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F101" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G101" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H101" s="19"/>
+      <c r="I101" s="19"/>
+      <c r="J101" s="20"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B102" s="15" t="s">
@@ -3341,18 +3319,18 @@
       <c r="D102" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E102" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F102" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G102" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
-      <c r="J102" s="21"/>
+      <c r="E102" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F102" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G102" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H102" s="19"/>
+      <c r="I102" s="19"/>
+      <c r="J102" s="20"/>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B103" s="15" t="s">
@@ -3364,18 +3342,18 @@
       <c r="D103" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F103" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G103" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
-      <c r="J103" s="21"/>
+      <c r="E103" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F103" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G103" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H103" s="19"/>
+      <c r="I103" s="19"/>
+      <c r="J103" s="20"/>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B104" s="15" t="s">
@@ -3387,18 +3365,18 @@
       <c r="D104" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E104" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="F104" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G104" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H104" s="20"/>
-      <c r="I104" s="20"/>
-      <c r="J104" s="21"/>
+      <c r="E104" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F104" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G104" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H104" s="19"/>
+      <c r="I104" s="19"/>
+      <c r="J104" s="20"/>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B105" s="15" t="s">
@@ -3410,18 +3388,18 @@
       <c r="D105" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E105" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F105" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G105" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H105" s="20"/>
-      <c r="I105" s="20"/>
-      <c r="J105" s="21"/>
+      <c r="E105" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F105" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G105" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H105" s="19"/>
+      <c r="I105" s="19"/>
+      <c r="J105" s="20"/>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B106" s="15" t="s">
@@ -3433,18 +3411,18 @@
       <c r="D106" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E106" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F106" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G106" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H106" s="20"/>
-      <c r="I106" s="20"/>
-      <c r="J106" s="21"/>
+      <c r="E106" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F106" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G106" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H106" s="19"/>
+      <c r="I106" s="19"/>
+      <c r="J106" s="20"/>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B107" s="15" t="s">
@@ -3456,18 +3434,18 @@
       <c r="D107" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="F107" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G107" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
-      <c r="J107" s="21"/>
+      <c r="E107" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F107" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G107" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H107" s="19"/>
+      <c r="I107" s="19"/>
+      <c r="J107" s="20"/>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B108" s="15" t="s">
@@ -3479,18 +3457,18 @@
       <c r="D108" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E108" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F108" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G108" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
-      <c r="J108" s="21"/>
+      <c r="E108" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F108" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G108" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="20"/>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B109" s="15" t="s">
@@ -3502,18 +3480,18 @@
       <c r="D109" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E109" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F109" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G109" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
-      <c r="J109" s="21"/>
+      <c r="E109" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F109" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G109" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H109" s="19"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="20"/>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B110" s="15" t="s">
@@ -3525,18 +3503,18 @@
       <c r="D110" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F110" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G110" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H110" s="20"/>
-      <c r="I110" s="20"/>
-      <c r="J110" s="21"/>
+      <c r="E110" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F110" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G110" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="20"/>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B111" s="15" t="s">
@@ -3548,18 +3526,18 @@
       <c r="D111" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F111" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G111" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
-      <c r="J111" s="21"/>
+      <c r="E111" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F111" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G111" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="20"/>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B112" s="15" t="s">
@@ -3571,18 +3549,18 @@
       <c r="D112" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F112" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G112" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H112" s="20"/>
-      <c r="I112" s="20"/>
-      <c r="J112" s="21"/>
+      <c r="E112" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F112" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G112" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H112" s="19"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="20"/>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B113" s="15" t="s">
@@ -3594,18 +3572,18 @@
       <c r="D113" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E113" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="F113" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G113" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
-      <c r="J113" s="21"/>
+      <c r="E113" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F113" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G113" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H113" s="19"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="20"/>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B114" s="15" t="s">
@@ -3617,18 +3595,18 @@
       <c r="D114" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E114" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F114" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G114" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H114" s="20"/>
-      <c r="I114" s="20"/>
-      <c r="J114" s="21"/>
+      <c r="E114" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F114" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G114" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="20"/>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B115" s="15" t="s">
@@ -3640,18 +3618,18 @@
       <c r="D115" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E115" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F115" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G115" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H115" s="20"/>
-      <c r="I115" s="20"/>
-      <c r="J115" s="21"/>
+      <c r="E115" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F115" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G115" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H115" s="19"/>
+      <c r="I115" s="19"/>
+      <c r="J115" s="20"/>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B116" s="15" t="s">
@@ -3663,18 +3641,18 @@
       <c r="D116" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E116" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F116" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G116" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
-      <c r="J116" s="21"/>
+      <c r="E116" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F116" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G116" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H116" s="19"/>
+      <c r="I116" s="19"/>
+      <c r="J116" s="20"/>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B117" s="15" t="s">
@@ -3686,18 +3664,18 @@
       <c r="D117" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E117" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F117" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G117" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
-      <c r="J117" s="21"/>
+      <c r="E117" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F117" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G117" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H117" s="19"/>
+      <c r="I117" s="19"/>
+      <c r="J117" s="20"/>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B118" s="15" t="s">
@@ -3709,18 +3687,18 @@
       <c r="D118" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E118" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F118" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G118" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
-      <c r="J118" s="21"/>
+      <c r="E118" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F118" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G118" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H118" s="19"/>
+      <c r="I118" s="19"/>
+      <c r="J118" s="20"/>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B119" s="15" t="s">
@@ -3732,18 +3710,18 @@
       <c r="D119" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E119" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="F119" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G119" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
-      <c r="J119" s="21"/>
+      <c r="E119" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F119" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G119" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="20"/>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B120" s="15" t="s">
@@ -3755,18 +3733,18 @@
       <c r="D120" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E120" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F120" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G120" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
-      <c r="J120" s="21"/>
+      <c r="E120" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="F120" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G120" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H120" s="19"/>
+      <c r="I120" s="19"/>
+      <c r="J120" s="20"/>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B121" s="15" t="s">
@@ -3778,18 +3756,18 @@
       <c r="D121" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E121" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F121" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G121" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
-      <c r="J121" s="21"/>
+      <c r="E121" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F121" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G121" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H121" s="19"/>
+      <c r="I121" s="19"/>
+      <c r="J121" s="20"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B122" s="15" t="s">
@@ -3801,18 +3779,18 @@
       <c r="D122" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E122" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="F122" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G122" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
-      <c r="J122" s="21"/>
+      <c r="E122" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F122" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G122" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H122" s="19"/>
+      <c r="I122" s="19"/>
+      <c r="J122" s="20"/>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B123" s="15" t="s">
@@ -3824,18 +3802,18 @@
       <c r="D123" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E123" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F123" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G123" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
-      <c r="J123" s="21"/>
+      <c r="E123" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="F123" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G123" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H123" s="19"/>
+      <c r="I123" s="19"/>
+      <c r="J123" s="20"/>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B124" s="15" t="s">
@@ -3847,18 +3825,18 @@
       <c r="D124" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E124" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F124" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G124" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H124" s="20"/>
-      <c r="I124" s="20"/>
-      <c r="J124" s="21"/>
+      <c r="E124" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F124" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G124" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H124" s="19"/>
+      <c r="I124" s="19"/>
+      <c r="J124" s="20"/>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B125" s="15" t="s">
@@ -3870,162 +3848,70 @@
       <c r="D125" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F125" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G125" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H125" s="20"/>
-      <c r="I125" s="20"/>
-      <c r="J125" s="21"/>
+      <c r="E125" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F125" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G125" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H125" s="19"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="20"/>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B126" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E126" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="F126" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G126" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
-      <c r="J126" s="21"/>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B127" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E127" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F127" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G127" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
-      <c r="J127" s="21"/>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B128" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C128" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="18" t="s">
+      <c r="B126" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="F128" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G128" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
-      <c r="J128" s="21"/>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B129" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F129" s="19">
-        <v>23580</v>
-      </c>
-      <c r="G129" s="19">
-        <v>589500</v>
-      </c>
-      <c r="H129" s="20"/>
-      <c r="I129" s="20"/>
-      <c r="J129" s="21"/>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B130" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C130" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="D130" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E130" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="F130" s="26">
-        <v>46400</v>
-      </c>
-      <c r="G130" s="26">
-        <v>1460000</v>
-      </c>
-      <c r="H130" s="27"/>
-      <c r="I130" s="27"/>
-      <c r="J130" s="28"/>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B135" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="C135" s="34"/>
-      <c r="H135" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1"/>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B136" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="C136" s="34"/>
-      <c r="H136" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
+      <c r="F126" s="24">
+        <v>23580</v>
+      </c>
+      <c r="G126" s="24">
+        <v>589500</v>
+      </c>
+      <c r="H126" s="25"/>
+      <c r="I126" s="25"/>
+      <c r="J126" s="26"/>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B131" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C131" s="32"/>
+      <c r="H131" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B132" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C132" s="32"/>
+      <c r="H132" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="H136:J136"/>
-    <mergeCell ref="H135:J135"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="H132:J132"/>
+    <mergeCell ref="H131:J131"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>

--- a/Data/EC/NIT-9006325466.xlsx
+++ b/Data/EC/NIT-9006325466.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D89DF95-9CE1-43B2-A85A-AB3DFEB72153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{581E2439-4C2E-430C-9F89-F24277D65176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3B49F944-E07D-4EB9-93A7-0FB1201A05E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4D513F85-CAE7-4CFE-93F9-E82E670B3EFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="141">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,252 +71,354 @@
     <t>ENRIQUE RUIZ GOMEZ</t>
   </si>
   <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
   </si>
   <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
     <t>PPT</t>
   </si>
   <si>
@@ -324,90 +426,6 @@
   </si>
   <si>
     <t>OSMEL JESUS DIAZ GONZALEZ</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -506,9 +524,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -521,7 +537,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -721,23 +739,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -765,10 +783,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -806,22 +824,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612B1EB2-8472-83BF-7D8B-26DE3E788F66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{263FDCBA-F2A0-CA76-ECC7-2679BF4ECF79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -843,7 +861,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1172,27 +1190,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6948C09F-7812-42E2-9EE3-896BC8EE18FC}">
-  <dimension ref="B2:J132"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C00587F-A818-4AF6-96E6-72EDF8EC91D4}">
+  <dimension ref="B2:J138"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1201,7 +1219,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1212,7 +1230,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1223,7 +1241,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1234,10 +1252,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1250,8 +1268,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1266,15 +1284,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2640200</v>
+        <v>2781680</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1282,27 +1300,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F13" s="5">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1322,16 +1340,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1354,7 +1372,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1377,7 +1395,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1400,7 +1418,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1423,7 +1441,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1446,7 +1464,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1469,7 +1487,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1492,7 +1510,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1515,7 +1533,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1538,7 +1556,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1561,7 +1579,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1584,7 +1602,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1607,7 +1625,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1630,7 +1648,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1653,7 +1671,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1676,7 +1694,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1699,7 +1717,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1722,7 +1740,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1745,7 +1763,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1768,7 +1786,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1791,7 +1809,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1814,7 +1832,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1837,7 +1855,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1860,7 +1878,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1883,7 +1901,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1906,7 +1924,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1929,7 +1947,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1952,7 +1970,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1975,7 +1993,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1998,7 +2016,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -2021,7 +2039,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -2044,7 +2062,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2067,7 +2085,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2090,7 +2108,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2113,7 +2131,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2136,7 +2154,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2159,7 +2177,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2182,7 +2200,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2205,7 +2223,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2228,7 +2246,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2251,7 +2269,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2274,7 +2292,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2297,7 +2315,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2320,7 +2338,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2343,7 +2361,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2366,7 +2384,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2389,7 +2407,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2412,7 +2430,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2435,7 +2453,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2458,7 +2476,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2481,7 +2499,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2504,7 +2522,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2527,7 +2545,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2550,7 +2568,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2573,7 +2591,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2596,7 +2614,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2619,7 +2637,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2642,7 +2660,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2665,7 +2683,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2688,7 +2706,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2711,7 +2729,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2734,7 +2752,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2757,7 +2775,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2780,7 +2798,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2803,7 +2821,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2826,7 +2844,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2849,7 +2867,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2872,7 +2890,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2895,7 +2913,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2918,7 +2936,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2941,7 +2959,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2964,7 +2982,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2987,7 +3005,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -3010,7 +3028,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -3033,7 +3051,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3056,7 +3074,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3079,7 +3097,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3102,7 +3120,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3125,7 +3143,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3148,7 +3166,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3171,7 +3189,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3194,7 +3212,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3217,30 +3235,30 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C98" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D98" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>92</v>
-      </c>
       <c r="F98" s="18">
-        <v>46400</v>
+        <v>23580</v>
       </c>
       <c r="G98" s="18">
-        <v>1460000</v>
+        <v>589500</v>
       </c>
       <c r="H98" s="19"/>
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3251,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F99" s="18">
         <v>23580</v>
@@ -3263,7 +3281,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3274,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F100" s="18">
         <v>23580</v>
@@ -3286,7 +3304,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3297,7 +3315,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F101" s="18">
         <v>23580</v>
@@ -3309,7 +3327,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3320,7 +3338,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F102" s="18">
         <v>23580</v>
@@ -3332,7 +3350,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3343,7 +3361,7 @@
         <v>10</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F103" s="18">
         <v>23580</v>
@@ -3355,7 +3373,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3366,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F104" s="18">
         <v>23580</v>
@@ -3378,7 +3396,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3389,7 +3407,7 @@
         <v>10</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F105" s="18">
         <v>23580</v>
@@ -3401,7 +3419,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3412,7 +3430,7 @@
         <v>10</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F106" s="18">
         <v>23580</v>
@@ -3424,7 +3442,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3435,7 +3453,7 @@
         <v>10</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F107" s="18">
         <v>23580</v>
@@ -3447,7 +3465,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3458,7 +3476,7 @@
         <v>10</v>
       </c>
       <c r="E108" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F108" s="18">
         <v>23580</v>
@@ -3470,7 +3488,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3481,7 +3499,7 @@
         <v>10</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F109" s="18">
         <v>23580</v>
@@ -3493,7 +3511,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3504,7 +3522,7 @@
         <v>10</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F110" s="18">
         <v>23580</v>
@@ -3516,7 +3534,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3527,7 +3545,7 @@
         <v>10</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F111" s="18">
         <v>23580</v>
@@ -3539,7 +3557,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3550,7 +3568,7 @@
         <v>10</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F112" s="18">
         <v>23580</v>
@@ -3562,7 +3580,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3573,7 +3591,7 @@
         <v>10</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F113" s="18">
         <v>23580</v>
@@ -3585,7 +3603,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3596,7 +3614,7 @@
         <v>10</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F114" s="18">
         <v>23580</v>
@@ -3608,7 +3626,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3619,7 +3637,7 @@
         <v>10</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F115" s="18">
         <v>23580</v>
@@ -3631,7 +3649,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3642,7 +3660,7 @@
         <v>10</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F116" s="18">
         <v>23580</v>
@@ -3654,7 +3672,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3665,7 +3683,7 @@
         <v>10</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F117" s="18">
         <v>23580</v>
@@ -3677,7 +3695,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3688,7 +3706,7 @@
         <v>10</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F118" s="18">
         <v>23580</v>
@@ -3700,7 +3718,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3711,7 +3729,7 @@
         <v>10</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F119" s="18">
         <v>23580</v>
@@ -3723,7 +3741,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3734,7 +3752,7 @@
         <v>10</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F120" s="18">
         <v>23580</v>
@@ -3746,7 +3764,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3757,7 +3775,7 @@
         <v>10</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F121" s="18">
         <v>23580</v>
@@ -3769,7 +3787,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3780,7 +3798,7 @@
         <v>10</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F122" s="18">
         <v>23580</v>
@@ -3792,7 +3810,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3803,7 +3821,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F123" s="18">
         <v>23580</v>
@@ -3815,7 +3833,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3826,7 +3844,7 @@
         <v>10</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F124" s="18">
         <v>23580</v>
@@ -3838,7 +3856,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3849,7 +3867,7 @@
         <v>10</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F125" s="18">
         <v>23580</v>
@@ -3861,57 +3879,195 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B126" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E126" s="22" t="s">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B126" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F126" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G126" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="20"/>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B127" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F127" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G127" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="20"/>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B128" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F126" s="24">
-        <v>23580</v>
-      </c>
-      <c r="G126" s="24">
-        <v>589500</v>
-      </c>
-      <c r="H126" s="25"/>
-      <c r="I126" s="25"/>
-      <c r="J126" s="26"/>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B131" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="C131" s="32"/>
-      <c r="H131" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B132" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="C132" s="32"/>
-      <c r="H132" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
+      <c r="F128" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G128" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="20"/>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B129" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F129" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G129" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H129" s="19"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="20"/>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B130" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F130" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G130" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="20"/>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B131" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F131" s="18">
+        <v>23580</v>
+      </c>
+      <c r="G131" s="18">
+        <v>589500</v>
+      </c>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="20"/>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B132" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C132" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D132" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F132" s="24">
+        <v>46400</v>
+      </c>
+      <c r="G132" s="24">
+        <v>1460000</v>
+      </c>
+      <c r="H132" s="25"/>
+      <c r="I132" s="25"/>
+      <c r="J132" s="26"/>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B137" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C137" s="32"/>
+      <c r="H137" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B138" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C138" s="32"/>
+      <c r="H138" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="H132:J132"/>
-    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="H138:J138"/>
+    <mergeCell ref="H137:J137"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
